--- a/backend/elderlycare-common/src/main/resources/excel_model/ServiceAssignment.xlsx
+++ b/backend/elderlycare-common/src/main/resources/excel_model/ServiceAssignment.xlsx
@@ -442,13 +442,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,11 +466,6 @@
           <t>备注</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -489,11 +483,6 @@
           <t>remark</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>operation</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -511,11 +500,6 @@
           <t>张管家负责张福顺日常服务</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>编辑</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -533,11 +517,6 @@
           <t>张管家负责李桂兰日常服务</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>编辑</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -553,11 +532,6 @@
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>王管家负责王建国康复服务</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>编辑</t>
         </is>
       </c>
     </row>
